--- a/salidas/empresas/GLW.xlsx
+++ b/salidas/empresas/GLW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.94624996185303</v>
+        <v>15.94625282287598</v>
       </c>
       <c r="C2" t="n">
         <v>24.35000038146973</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>15.98554134368896</v>
+        <v>15.98554706573486</v>
       </c>
       <c r="C3" t="n">
         <v>24.40999984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.62928009033203</v>
+        <v>17.62928199768066</v>
       </c>
       <c r="C4" t="n">
         <v>26.92000007629395</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>18.09424591064453</v>
+        <v>18.0942440032959</v>
       </c>
       <c r="C5" t="n">
         <v>27.6299991607666</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.88076019287109</v>
+        <v>15.88076305389404</v>
       </c>
       <c r="C6" t="n">
         <v>24.25</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>15.84147548675537</v>
+        <v>15.84146595001221</v>
       </c>
       <c r="C7" t="n">
         <v>24.19000053405762</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.48850250244141</v>
+        <v>12.48849964141846</v>
       </c>
       <c r="C8" t="n">
         <v>19.06999969482422</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>15.98554134368896</v>
+        <v>15.98554706573486</v>
       </c>
       <c r="C10" t="n">
         <v>24.40999984741211</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>13.37913036346436</v>
+        <v>13.37914276123047</v>
       </c>
       <c r="C11" t="n">
         <v>20.43000030517578</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.11913871765137</v>
+        <v>14.11914443969727</v>
       </c>
       <c r="C12" t="n">
         <v>21.55999946594238</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.25274562835693</v>
+        <v>12.25274848937988</v>
       </c>
       <c r="C13" t="n">
         <v>18.70999908447266</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.64763069152832</v>
+        <v>13.64763450622559</v>
       </c>
       <c r="C14" t="n">
         <v>20.84000015258789</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.51010799407959</v>
+        <v>13.51010513305664</v>
       </c>
       <c r="C15" t="n">
         <v>20.6299991607666</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.89189910888672</v>
+        <v>14.89189338684082</v>
       </c>
       <c r="C16" t="n">
         <v>22.73999977111816</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>15.5336742401123</v>
+        <v>15.53367233276367</v>
       </c>
       <c r="C17" t="n">
         <v>23.71999931335449</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>16.37191963195801</v>
+        <v>16.37191200256348</v>
       </c>
       <c r="C18" t="n">
         <v>25</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.73209381103516</v>
+        <v>16.73210525512695</v>
       </c>
       <c r="C19" t="n">
         <v>25.54999923706055</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.61225700378418</v>
+        <v>15.61226654052734</v>
       </c>
       <c r="C20" t="n">
         <v>23.84000015258789</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>15.33646678924561</v>
+        <v>15.33645915985107</v>
       </c>
       <c r="C21" t="n">
         <v>23.3700008392334</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.17645263671875</v>
+        <v>16.17645454406738</v>
       </c>
       <c r="C22" t="n">
         <v>24.64999961853027</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.92708301544189</v>
+        <v>15.92708683013916</v>
       </c>
       <c r="C23" t="n">
         <v>24.27000045776367</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.97746181488037</v>
+        <v>15.97744750976562</v>
       </c>
       <c r="C24" t="n">
         <v>24.29000091552734</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.78011798858643</v>
+        <v>15.78011894226074</v>
       </c>
       <c r="C25" t="n">
         <v>23.98999977111816</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.89194488525391</v>
+        <v>15.89193439483643</v>
       </c>
       <c r="C26" t="n">
         <v>24.15999984741211</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.84589195251465</v>
+        <v>15.8459005355835</v>
       </c>
       <c r="C28" t="n">
         <v>24.04000091552734</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>17.60581207275391</v>
+        <v>17.60582542419434</v>
       </c>
       <c r="C29" t="n">
         <v>26.70999908447266</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>18.05387496948242</v>
+        <v>18.05386924743652</v>
       </c>
       <c r="C30" t="n">
         <v>27.34000015258789</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>15.22098445892334</v>
+        <v>15.22098827362061</v>
       </c>
       <c r="C31" t="n">
         <v>23.04999923706055</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>10.35253620147705</v>
+        <v>10.35253429412842</v>
       </c>
       <c r="C34" t="n">
         <v>15.64000034332275</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>7.168668746948242</v>
+        <v>7.168665409088135</v>
       </c>
       <c r="C35" t="n">
         <v>10.82999992370605</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>5.996693134307861</v>
+        <v>5.996695995330811</v>
       </c>
       <c r="C36" t="n">
         <v>9.010000228881836</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>6.342784881591797</v>
+        <v>6.342786312103271</v>
       </c>
       <c r="C37" t="n">
         <v>9.529999732971191</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.72880744934082</v>
+        <v>6.72881031036377</v>
       </c>
       <c r="C38" t="n">
         <v>10.10999965667725</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>7.055542945861816</v>
+        <v>7.055545806884766</v>
       </c>
       <c r="C39" t="n">
         <v>10.55000019073486</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.777446746826172</v>
+        <v>9.777445793151855</v>
       </c>
       <c r="C41" t="n">
         <v>14.61999988555908</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.77733421325684</v>
+        <v>10.77733516693115</v>
       </c>
       <c r="C43" t="n">
         <v>16.05999946594238</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.40814304351807</v>
+        <v>11.40813732147217</v>
       </c>
       <c r="C44" t="n">
         <v>17</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>10.15131568908691</v>
+        <v>10.15131759643555</v>
       </c>
       <c r="C45" t="n">
         <v>15.07999992370605</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>10.30614280700684</v>
+        <v>10.30614566802979</v>
       </c>
       <c r="C46" t="n">
         <v>15.3100004196167</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.834928512573242</v>
+        <v>9.834927558898926</v>
       </c>
       <c r="C47" t="n">
         <v>14.60999965667725</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>11.26294803619385</v>
+        <v>11.2629451751709</v>
       </c>
       <c r="C48" t="n">
         <v>16.68000030517578</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.03881645202637</v>
+        <v>13.03881740570068</v>
       </c>
       <c r="C49" t="n">
         <v>19.30999946594238</v>
@@ -1430,7 +1442,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>11.93910884857178</v>
+        <v>11.93910694122314</v>
       </c>
       <c r="C51" t="n">
         <v>17.6299991607666</v>
@@ -1480,7 +1492,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.03617572784424</v>
+        <v>13.03618144989014</v>
       </c>
       <c r="C53" t="n">
         <v>19.25</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>11.83858966827393</v>
+        <v>11.83859252929688</v>
       </c>
       <c r="C54" t="n">
         <v>17.43000030517578</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>10.96920299530029</v>
+        <v>10.96920394897461</v>
       </c>
       <c r="C55" t="n">
         <v>16.14999961853027</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.30724430084229</v>
+        <v>12.30724239349365</v>
       </c>
       <c r="C56" t="n">
         <v>18.1200008392334</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>10.68298816680908</v>
+        <v>10.68299198150635</v>
       </c>
       <c r="C57" t="n">
         <v>15.68000030517578</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.45440673828125</v>
+        <v>12.45440578460693</v>
       </c>
       <c r="C58" t="n">
         <v>18.28000068664551</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>12.45440673828125</v>
+        <v>12.45440578460693</v>
       </c>
       <c r="C59" t="n">
         <v>18.28000068664551</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>12.06482982635498</v>
+        <v>12.0648307800293</v>
       </c>
       <c r="C60" t="n">
         <v>17.65999984741211</v>
@@ -1705,7 +1717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1730,7 +1742,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.78923606872559</v>
+        <v>15.78923320770264</v>
       </c>
       <c r="C63" t="n">
         <v>23.05999946594238</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>14.12541007995605</v>
+        <v>14.125412940979</v>
       </c>
       <c r="C64" t="n">
         <v>20.6299991607666</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>14.33766746520996</v>
+        <v>14.33766937255859</v>
       </c>
       <c r="C65" t="n">
         <v>20.94000053405762</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.83207607269287</v>
+        <v>13.83208084106445</v>
       </c>
       <c r="C66" t="n">
         <v>20.14999961853027</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>12.45916652679443</v>
+        <v>12.45916557312012</v>
       </c>
       <c r="C67" t="n">
         <v>18.14999961853027</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>10.92150592803955</v>
+        <v>10.92150497436523</v>
       </c>
       <c r="C68" t="n">
         <v>15.90999984741211</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>10.3534460067749</v>
+        <v>10.35344791412354</v>
       </c>
       <c r="C69" t="n">
         <v>15.02999973297119</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>8.514211654663086</v>
+        <v>8.514214515686035</v>
       </c>
       <c r="C70" t="n">
         <v>12.35999965667725</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.843697547912598</v>
+        <v>9.843698501586914</v>
       </c>
       <c r="C71" t="n">
         <v>14.28999996185303</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>9.186428070068359</v>
+        <v>9.186427116394043</v>
       </c>
       <c r="C72" t="n">
         <v>13.27000045776367</v>
@@ -2045,7 +2057,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>8.909519195556641</v>
+        <v>8.909516334533691</v>
       </c>
       <c r="C74" t="n">
         <v>12.86999988555908</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.076712608337402</v>
+        <v>9.07671070098877</v>
       </c>
       <c r="C75" t="n">
         <v>13.03999996185303</v>
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>9.988558769226074</v>
+        <v>9.988559722900391</v>
       </c>
       <c r="C77" t="n">
         <v>14.35000038146973</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.094743728637695</v>
+        <v>9.094744682312012</v>
       </c>
       <c r="C78" t="n">
         <v>12.98999977111816</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>9.052741050720215</v>
+        <v>9.052742004394531</v>
       </c>
       <c r="C79" t="n">
         <v>12.93000030517578</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>7.98853063583374</v>
+        <v>7.988532543182373</v>
       </c>
       <c r="C80" t="n">
         <v>11.40999984741211</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>8.448860168457031</v>
+        <v>8.44886302947998</v>
       </c>
       <c r="C81" t="n">
         <v>11.98999977111816</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>9.266264915466309</v>
+        <v>9.266267776489258</v>
       </c>
       <c r="C82" t="n">
         <v>13.14999961853027</v>
@@ -2335,7 +2347,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>8.965096473693848</v>
+        <v>8.965097427368164</v>
       </c>
       <c r="C85" t="n">
         <v>12.61999988555908</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>8.524660110473633</v>
+        <v>8.524656295776367</v>
       </c>
       <c r="C86" t="n">
         <v>12</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>9.02375316619873</v>
+        <v>9.023754119873047</v>
       </c>
       <c r="C87" t="n">
         <v>12.60999965667725</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.538985252380371</v>
+        <v>9.538989067077637</v>
       </c>
       <c r="C88" t="n">
         <v>13.32999992370605</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>10.37624168395996</v>
+        <v>10.37624740600586</v>
       </c>
       <c r="C89" t="n">
         <v>14.5</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>11.06905078887939</v>
+        <v>11.06905174255371</v>
       </c>
       <c r="C90" t="n">
         <v>15.36999988555908</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>10.24805450439453</v>
+        <v>10.24805545806885</v>
       </c>
       <c r="C91" t="n">
         <v>14.22999954223633</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>10.93941974639893</v>
+        <v>10.93942356109619</v>
       </c>
       <c r="C92" t="n">
         <v>15.1899995803833</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>10.18283367156982</v>
+        <v>10.18283271789551</v>
       </c>
       <c r="C93" t="n">
         <v>14.03999996185303</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.58173084259033</v>
+        <v>10.58172988891602</v>
       </c>
       <c r="C94" t="n">
         <v>14.59000015258789</v>
@@ -2683,7 +2695,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.46215152740479</v>
+        <v>12.46215629577637</v>
       </c>
       <c r="C96" t="n">
         <v>17.07999992370605</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>13.00208568572998</v>
+        <v>13.00208187103271</v>
       </c>
       <c r="C97" t="n">
         <v>17.81999969482422</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>12.55700302124023</v>
+        <v>12.55700588226318</v>
       </c>
       <c r="C98" t="n">
         <v>17.20999908447266</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>14.1333532333374</v>
+        <v>14.13335132598877</v>
       </c>
       <c r="C99" t="n">
         <v>19.27000045776367</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>15.27018642425537</v>
+        <v>15.27018356323242</v>
       </c>
       <c r="C100" t="n">
         <v>20.81999969482422</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>15.33619499206543</v>
+        <v>15.3361930847168</v>
       </c>
       <c r="C101" t="n">
         <v>20.90999984741211</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>15.69543933868408</v>
+        <v>15.69544315338135</v>
       </c>
       <c r="C102" t="n">
         <v>21.29999923706055</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>16.17441368103027</v>
+        <v>16.17440986633301</v>
       </c>
       <c r="C103" t="n">
         <v>21.95000076293945</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>14.47960090637207</v>
+        <v>14.47959804534912</v>
       </c>
       <c r="C104" t="n">
         <v>19.64999961853027</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>15.44569492340088</v>
+        <v>15.44569110870361</v>
       </c>
       <c r="C105" t="n">
         <v>20.86000061035156</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>14.32020950317383</v>
+        <v>14.32021522521973</v>
       </c>
       <c r="C106" t="n">
         <v>19.34000015258789</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>15.12729835510254</v>
+        <v>15.12730121612549</v>
       </c>
       <c r="C107" t="n">
         <v>20.43000030517578</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>15.63931560516357</v>
+        <v>15.63931083679199</v>
       </c>
       <c r="C108" t="n">
         <v>21.02000045776367</v>
@@ -3089,7 +3101,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>17.68537330627441</v>
+        <v>17.68536949157715</v>
       </c>
       <c r="C110" t="n">
         <v>23.77000045776367</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>18.24244499206543</v>
+        <v>18.24244117736816</v>
       </c>
       <c r="C111" t="n">
         <v>24.39999961853027</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>16.95649909973145</v>
+        <v>16.95650100708008</v>
       </c>
       <c r="C112" t="n">
         <v>22.68000030517578</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>15.64813137054443</v>
+        <v>15.64813041687012</v>
       </c>
       <c r="C113" t="n">
         <v>20.93000030517578</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>15.72964668273926</v>
+        <v>15.72965240478516</v>
       </c>
       <c r="C114" t="n">
         <v>20.92000007629395</v>
@@ -3263,7 +3275,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>14.04540634155273</v>
+        <v>14.04540538787842</v>
       </c>
       <c r="C116" t="n">
         <v>18.68000030517578</v>
@@ -3321,7 +3333,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.96663856506348</v>
+        <v>12.96663570404053</v>
       </c>
       <c r="C118" t="n">
         <v>17.1200008392334</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>14.08758640289307</v>
+        <v>14.0875825881958</v>
       </c>
       <c r="C119" t="n">
         <v>18.60000038146973</v>
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.93429946899414</v>
+        <v>13.93429756164551</v>
       </c>
       <c r="C121" t="n">
         <v>18.28000068664551</v>
@@ -3466,7 +3478,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>14.05103969573975</v>
+        <v>14.05103778839111</v>
       </c>
       <c r="C123" t="n">
         <v>18.29999923706055</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>16.03968238830566</v>
+        <v>16.0396842956543</v>
       </c>
       <c r="C124" t="n">
         <v>20.88999938964844</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>14.33512878417969</v>
+        <v>14.33512783050537</v>
       </c>
       <c r="C125" t="n">
         <v>18.67000007629395</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>16.1486873626709</v>
+        <v>16.14868927001953</v>
       </c>
       <c r="C126" t="n">
         <v>20.88999938964844</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>15.83173847198486</v>
+        <v>15.83174610137939</v>
       </c>
       <c r="C127" t="n">
         <v>20.47999954223633</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>17.17682456970215</v>
+        <v>17.17682266235352</v>
       </c>
       <c r="C128" t="n">
         <v>22.21999931335449</v>
@@ -3669,7 +3681,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>17.66077995300293</v>
+        <v>17.66077613830566</v>
       </c>
       <c r="C131" t="n">
         <v>22.70999908447266</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>18.79531288146973</v>
+        <v>18.79531478881836</v>
       </c>
       <c r="C132" t="n">
         <v>24.03000068664551</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>18.98303985595703</v>
+        <v>18.98303604125977</v>
       </c>
       <c r="C133" t="n">
         <v>24.27000045776367</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>20.71942901611328</v>
+        <v>20.71942520141602</v>
       </c>
       <c r="C134" t="n">
         <v>26.48999977111816</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>21.71758842468262</v>
+        <v>21.71759223937988</v>
       </c>
       <c r="C135" t="n">
         <v>27.61000061035156</v>
@@ -3872,7 +3884,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>22.69296264648438</v>
+        <v>22.69295883178711</v>
       </c>
       <c r="C137" t="n">
         <v>28.85000038146973</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>23.01021766662598</v>
+        <v>23.01022148132324</v>
       </c>
       <c r="C138" t="n">
         <v>29.10000038146973</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>23.76140594482422</v>
+        <v>23.76141166687012</v>
       </c>
       <c r="C139" t="n">
         <v>30.04999923706055</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>23.04184532165527</v>
+        <v>23.04184341430664</v>
       </c>
       <c r="C140" t="n">
         <v>29.13999938964844</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>22.86459541320801</v>
+        <v>22.86459350585938</v>
       </c>
       <c r="C141" t="n">
         <v>28.76000022888184</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>23.78680801391602</v>
+        <v>23.78681373596191</v>
       </c>
       <c r="C142" t="n">
         <v>29.92000007629395</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>24.89187812805176</v>
+        <v>24.89188003540039</v>
       </c>
       <c r="C143" t="n">
         <v>31.30999946594238</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>25.87702751159668</v>
+        <v>25.87702369689941</v>
       </c>
       <c r="C144" t="n">
         <v>32.38999938964844</v>
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>24.94229125976562</v>
+        <v>24.94228553771973</v>
       </c>
       <c r="C146" t="n">
         <v>31.21999931335449</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>23.37364387512207</v>
+        <v>23.37363815307617</v>
       </c>
       <c r="C147" t="n">
         <v>29.07999992370605</v>
@@ -4218,7 +4230,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4245,7 +4257,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>21.98644065856934</v>
+        <v>21.98644256591797</v>
       </c>
       <c r="C150" t="n">
         <v>27.17000007629395</v>
@@ -4299,11 +4311,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>22.26157569885254</v>
+        <v>22.26157760620117</v>
       </c>
       <c r="C151" t="n">
         <v>27.51000022888184</v>
@@ -4326,7 +4338,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4353,11 +4365,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>27.26202201843262</v>
+        <v>27.26201820373535</v>
       </c>
       <c r="C153" t="n">
         <v>33.5099983215332</v>
@@ -4380,11 +4392,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>28.7182731628418</v>
+        <v>28.71827697753906</v>
       </c>
       <c r="C154" t="n">
         <v>35.29999923706055</v>
@@ -4407,11 +4419,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>25.99288368225098</v>
+        <v>25.99288558959961</v>
       </c>
       <c r="C155" t="n">
         <v>31.95000076293945</v>
@@ -4434,11 +4446,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>26.36276054382324</v>
+        <v>26.36275863647461</v>
       </c>
       <c r="C156" t="n">
         <v>32.22000122070312</v>
@@ -4461,11 +4473,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>24.71815299987793</v>
+        <v>24.7181568145752</v>
       </c>
       <c r="C157" t="n">
         <v>30.20999908447266</v>
@@ -4488,11 +4500,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.21369743347168</v>
+        <v>27.21370506286621</v>
       </c>
       <c r="C158" t="n">
         <v>33.2599983215332</v>
@@ -4515,11 +4527,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>28.64603614807129</v>
+        <v>28.64604187011719</v>
       </c>
       <c r="C159" t="n">
         <v>34.81000137329102</v>
@@ -4544,7 +4556,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4573,11 +4585,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>26.21018409729004</v>
+        <v>26.21018028259277</v>
       </c>
       <c r="C161" t="n">
         <v>31.85000038146973</v>
@@ -4602,11 +4614,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>23.89691162109375</v>
+        <v>23.89690589904785</v>
       </c>
       <c r="C162" t="n">
         <v>28.84000015258789</v>
@@ -4631,11 +4643,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>27.53447151184082</v>
+        <v>27.53447532653809</v>
       </c>
       <c r="C163" t="n">
         <v>33.22999954223633</v>
@@ -4660,11 +4672,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.47953605651855</v>
+        <v>25.47953796386719</v>
       </c>
       <c r="C164" t="n">
         <v>30.75</v>
@@ -4689,11 +4701,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.24639701843262</v>
+        <v>23.24639892578125</v>
       </c>
       <c r="C165" t="n">
         <v>27.85000038146973</v>
@@ -4718,11 +4730,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>23.80564308166504</v>
+        <v>23.80564880371094</v>
       </c>
       <c r="C166" t="n">
         <v>28.52000045776367</v>
@@ -4747,11 +4759,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>24.73215866088867</v>
+        <v>24.7321605682373</v>
       </c>
       <c r="C167" t="n">
         <v>29.6299991607666</v>
@@ -4776,11 +4788,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>24.40622520446777</v>
+        <v>24.40622711181641</v>
       </c>
       <c r="C168" t="n">
         <v>29.04000091552734</v>
@@ -4805,11 +4817,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>24.46506309509277</v>
+        <v>24.46506118774414</v>
       </c>
       <c r="C169" t="n">
         <v>29.11000061035156</v>
@@ -4834,11 +4846,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>22.43120956420898</v>
+        <v>22.43120384216309</v>
       </c>
       <c r="C170" t="n">
         <v>26.69000053405762</v>
@@ -4863,11 +4875,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>20.22902679443359</v>
+        <v>20.22903060913086</v>
       </c>
       <c r="C171" t="n">
         <v>23.86000061035156</v>
@@ -4892,11 +4904,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>17.41425895690918</v>
+        <v>17.41425323486328</v>
       </c>
       <c r="C172" t="n">
         <v>20.54000091552734</v>
@@ -4921,7 +4933,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4950,7 +4962,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4979,11 +4991,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>22.16762542724609</v>
+        <v>22.16762351989746</v>
       </c>
       <c r="C175" t="n">
         <v>25.89999961853027</v>
@@ -5008,11 +5020,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>26.53268051147461</v>
+        <v>26.53267288208008</v>
       </c>
       <c r="C176" t="n">
         <v>31</v>
@@ -5037,11 +5049,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>27.97000122070312</v>
+        <v>27.96999549865723</v>
       </c>
       <c r="C177" t="n">
         <v>32.45999908447266</v>
@@ -5066,11 +5078,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>27.92691612243652</v>
+        <v>27.92691421508789</v>
       </c>
       <c r="C178" t="n">
         <v>32.40999984741211</v>
@@ -5095,7 +5107,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5124,11 +5136,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>32.44228363037109</v>
+        <v>32.44227981567383</v>
       </c>
       <c r="C180" t="n">
         <v>37.41999816894531</v>
@@ -5153,11 +5165,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>31.21117210388184</v>
+        <v>31.21116828918457</v>
       </c>
       <c r="C181" t="n">
         <v>36</v>
@@ -5182,11 +5194,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>31.09845924377441</v>
+        <v>31.09846496582031</v>
       </c>
       <c r="C182" t="n">
         <v>35.86999893188477</v>
@@ -5211,11 +5223,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>33.36046981811523</v>
+        <v>33.36045837402344</v>
       </c>
       <c r="C183" t="n">
         <v>38.2400016784668</v>
@@ -5240,11 +5252,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>37.95798873901367</v>
+        <v>37.95798492431641</v>
       </c>
       <c r="C184" t="n">
         <v>43.5099983215332</v>
@@ -5269,7 +5281,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5298,11 +5310,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>38.27244567871094</v>
+        <v>38.27243804931641</v>
       </c>
       <c r="C186" t="n">
         <v>43.63000106811523</v>
@@ -5327,11 +5339,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>35.87767791748047</v>
+        <v>35.87766647338867</v>
       </c>
       <c r="C187" t="n">
         <v>40.90000152587891</v>
@@ -5356,7 +5368,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5385,11 +5397,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>35.28723526000977</v>
+        <v>35.28725051879883</v>
       </c>
       <c r="C189" t="n">
         <v>39.9900016784668</v>
@@ -5414,7 +5426,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5443,11 +5455,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.38703346252441</v>
+        <v>31.38702774047852</v>
       </c>
       <c r="C191" t="n">
         <v>35.56999969482422</v>
@@ -5472,11 +5484,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>32.93509292602539</v>
+        <v>32.93508911132812</v>
       </c>
       <c r="C192" t="n">
         <v>37.09000015258789</v>
@@ -5501,11 +5513,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>33.05942153930664</v>
+        <v>33.05940628051758</v>
       </c>
       <c r="C193" t="n">
         <v>37.22999954223633</v>
@@ -5530,11 +5542,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>37.3305778503418</v>
+        <v>37.33058166503906</v>
       </c>
       <c r="C194" t="n">
         <v>42.04000091552734</v>
@@ -5559,11 +5571,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>36.11500930786133</v>
+        <v>36.1150016784668</v>
       </c>
       <c r="C195" t="n">
         <v>40.40000152587891</v>
@@ -5588,7 +5600,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5617,11 +5629,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>31.45760154724121</v>
+        <v>31.45759201049805</v>
       </c>
       <c r="C197" t="n">
         <v>35.18999862670898</v>
@@ -5646,11 +5658,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>32.26815032958984</v>
+        <v>32.26815795898438</v>
       </c>
       <c r="C198" t="n">
         <v>35.81999969482422</v>
@@ -5675,11 +5687,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>28.38552665710449</v>
+        <v>28.38552284240723</v>
       </c>
       <c r="C199" t="n">
         <v>31.51000022888184</v>
@@ -5704,11 +5716,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>33.11494064331055</v>
+        <v>33.11493682861328</v>
       </c>
       <c r="C200" t="n">
         <v>36.7599983215332</v>
@@ -5733,11 +5745,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>31.16175651550293</v>
+        <v>31.16175842285156</v>
       </c>
       <c r="C201" t="n">
         <v>34.31999969482422</v>
@@ -5762,11 +5774,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>26.3494815826416</v>
+        <v>26.34947776794434</v>
       </c>
       <c r="C202" t="n">
         <v>29.02000045776367</v>
@@ -5791,11 +5803,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>29.2096061706543</v>
+        <v>29.20960426330566</v>
       </c>
       <c r="C203" t="n">
         <v>32.16999816894531</v>
@@ -5820,11 +5832,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>31.24118995666504</v>
+        <v>31.24118804931641</v>
       </c>
       <c r="C204" t="n">
         <v>34.13000106811523</v>
@@ -5849,11 +5861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>29.23654937744141</v>
+        <v>29.23655128479004</v>
       </c>
       <c r="C205" t="n">
         <v>31.94000053405762</v>
@@ -5878,7 +5890,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5907,11 +5919,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>31.33212280273438</v>
+        <v>31.33212089538574</v>
       </c>
       <c r="C207" t="n">
         <v>33.95000076293945</v>
@@ -5936,11 +5948,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>32.55956268310547</v>
+        <v>32.5595588684082</v>
       </c>
       <c r="C208" t="n">
         <v>35.27999877929688</v>
@@ -5965,11 +5977,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>30.65840339660645</v>
+        <v>30.65840721130371</v>
       </c>
       <c r="C209" t="n">
         <v>33.22000122070312</v>
@@ -5994,7 +6006,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6023,11 +6035,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>32.62782287597656</v>
+        <v>32.62781524658203</v>
       </c>
       <c r="C211" t="n">
         <v>35.04000091552734</v>
@@ -6052,11 +6064,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>31.60354995727539</v>
+        <v>31.60354042053223</v>
       </c>
       <c r="C212" t="n">
         <v>33.93999862670898</v>
@@ -6081,7 +6093,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6110,7 +6122,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6139,7 +6151,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6168,11 +6180,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>27.01775360107422</v>
+        <v>27.01775550842285</v>
       </c>
       <c r="C216" t="n">
         <v>28.48999977111816</v>
@@ -6197,7 +6209,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6226,7 +6238,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6255,11 +6267,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>30.84024238586426</v>
+        <v>30.84024429321289</v>
       </c>
       <c r="C219" t="n">
         <v>32.2400016784668</v>
@@ -6284,11 +6296,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>31.52897644042969</v>
+        <v>31.52897834777832</v>
       </c>
       <c r="C220" t="n">
         <v>32.95999908447266</v>
@@ -6313,11 +6325,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>31.93074989318848</v>
+        <v>31.93074607849121</v>
       </c>
       <c r="C221" t="n">
         <v>33.38000106811523</v>
@@ -6342,11 +6354,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>35.91436767578125</v>
+        <v>35.91436386108398</v>
       </c>
       <c r="C222" t="n">
         <v>37.2599983215332</v>
@@ -6371,11 +6383,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>37.44694900512695</v>
+        <v>37.44694519042969</v>
       </c>
       <c r="C223" t="n">
         <v>38.84999847412109</v>
@@ -6400,11 +6412,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>38.56504821777344</v>
+        <v>38.5650520324707</v>
       </c>
       <c r="C224" t="n">
         <v>40.0099983215332</v>
@@ -6429,11 +6441,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>40.61017227172852</v>
+        <v>40.61017608642578</v>
       </c>
       <c r="C225" t="n">
         <v>41.84999847412109</v>
@@ -6458,7 +6470,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6487,11 +6499,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>46.18012619018555</v>
+        <v>46.18013000488281</v>
       </c>
       <c r="C227" t="n">
         <v>47.59000015258789</v>
@@ -6516,11 +6528,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>47.5108757019043</v>
+        <v>47.51087188720703</v>
       </c>
       <c r="C228" t="n">
         <v>48.66999816894531</v>
@@ -6545,11 +6557,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>46.38826751708984</v>
+        <v>46.38826370239258</v>
       </c>
       <c r="C229" t="n">
         <v>47.52000045776367</v>
@@ -6574,11 +6586,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>50.83966064453125</v>
+        <v>50.83966445922852</v>
       </c>
       <c r="C230" t="n">
         <v>52.08000183105469</v>
@@ -6603,11 +6615,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>49.23697662353516</v>
+        <v>49.23698425292969</v>
       </c>
       <c r="C231" t="n">
         <v>50.15000152587891</v>
@@ -6632,7 +6644,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6661,11 +6673,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>43.57202911376953</v>
+        <v>43.5720329284668</v>
       </c>
       <c r="C233" t="n">
         <v>44.38000106811523</v>
@@ -6690,7 +6702,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6719,11 +6731,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>51.92356872558594</v>
+        <v>51.92356491088867</v>
       </c>
       <c r="C235" t="n">
         <v>52.59000015258789</v>
@@ -6748,7 +6760,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6777,7 +6789,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6806,7 +6818,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6835,7 +6847,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6864,7 +6876,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6893,11 +6905,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>87.09912872314453</v>
+        <v>87.09912109375</v>
       </c>
       <c r="C241" t="n">
         <v>87.55999755859375</v>
@@ -6922,11 +6934,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>102.7065505981445</v>
+        <v>102.70654296875</v>
       </c>
       <c r="C242" t="n">
         <v>103.25</v>
@@ -6951,7 +6963,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6980,7 +6992,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7009,7 +7021,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7038,7 +7050,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7067,7 +7079,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7096,7 +7108,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7125,7 +7137,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7154,32 +7166,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>154.4799957275391</v>
+        <v>154.1499938964844</v>
       </c>
       <c r="C250" t="n">
-        <v>154.4799957275391</v>
+        <v>154.1499938964844</v>
       </c>
       <c r="D250" t="n">
-        <v>147157100</v>
+        <v>152581300</v>
       </c>
       <c r="E250" t="n">
         <v>2.18</v>
       </c>
       <c r="F250" t="n">
-        <v>70.86238336125645</v>
+        <v>70.71100637453411</v>
       </c>
       <c r="G250" t="n">
         <v>861388331</v>
       </c>
       <c r="H250" t="n">
-        <v>133067265692.632</v>
+        <v>132783005966.1529</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1708371180616794</v>
+        <v>0.17713416180466</v>
       </c>
     </row>
   </sheetData>
@@ -7211,75 +7223,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40119</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7483,13 +7495,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7525,13 +7537,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7567,13 +7579,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7609,13 +7621,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7642,7 +7654,7 @@
       <c r="I10" t="n">
         <v>2.25</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="K10" t="n">
@@ -7655,13 +7667,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7688,7 +7700,7 @@
       <c r="I11" t="n">
         <v>2.2</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="K11" t="n">
@@ -7701,13 +7713,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7734,7 +7746,7 @@
       <c r="I12" t="n">
         <v>2.09</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="K12" t="n">
@@ -7747,13 +7759,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7780,7 +7792,7 @@
       <c r="I13" t="n">
         <v>2.1</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K13" t="n">
@@ -7793,13 +7805,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7826,7 +7838,7 @@
       <c r="I14" t="n">
         <v>1.77</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K14" t="n">
@@ -7839,13 +7851,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7872,7 +7884,7 @@
       <c r="I15" t="n">
         <v>1.6</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="K15" t="n">
@@ -7885,13 +7897,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7918,7 +7930,7 @@
       <c r="I16" t="n">
         <v>1.43</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="K16" t="n">
@@ -7931,13 +7943,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7964,7 +7976,7 @@
       <c r="I17" t="n">
         <v>1.27</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="K17" t="n">
@@ -7977,13 +7989,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41318</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8010,7 +8022,7 @@
       <c r="I18" t="n">
         <v>1.15</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41318</v>
       </c>
       <c r="K18" t="n">
@@ -8023,13 +8035,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8056,7 +8068,7 @@
       <c r="I19" t="n">
         <v>1.18</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="K19" t="n">
@@ -8069,13 +8081,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8102,7 +8114,7 @@
       <c r="I20" t="n">
         <v>1.31</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K20" t="n">
@@ -8115,13 +8127,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8148,7 +8160,7 @@
       <c r="I21" t="n">
         <v>1.24</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K21" t="n">
@@ -8161,13 +8173,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8194,7 +8206,7 @@
       <c r="I22" t="n">
         <v>1.34</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="K22" t="n">
@@ -8207,13 +8219,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41757</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8240,7 +8252,7 @@
       <c r="I23" t="n">
         <v>1.21</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41757</v>
       </c>
       <c r="K23" t="n">
@@ -8253,13 +8265,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8286,7 +8298,7 @@
       <c r="I24" t="n">
         <v>0.89</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K24" t="n">
@@ -8299,13 +8311,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8332,7 +8344,7 @@
       <c r="I25" t="n">
         <v>1.33</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K25" t="n">
@@ -8345,13 +8357,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8378,7 +8390,7 @@
       <c r="I26" t="n">
         <v>1.73</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="K26" t="n">
@@ -8391,13 +8403,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8424,7 +8436,7 @@
       <c r="I27" t="n">
         <v>1.82</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K27" t="n">
@@ -8437,13 +8449,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8470,7 +8482,7 @@
       <c r="I28" t="n">
         <v>2.07</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K28" t="n">
@@ -8483,13 +8495,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8516,7 +8528,7 @@
       <c r="I29" t="n">
         <v>1.5</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="K29" t="n">
@@ -8529,13 +8541,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8562,7 +8574,7 @@
       <c r="I30" t="n">
         <v>0.97</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="K30" t="n">
@@ -8575,13 +8587,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8608,7 +8620,7 @@
       <c r="I31" t="n">
         <v>0.32</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K31" t="n">
@@ -8621,13 +8633,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8654,7 +8666,7 @@
       <c r="I32" t="n">
         <v>1.83</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="K32" t="n">
@@ -8667,13 +8679,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8700,7 +8712,7 @@
       <c r="I33" t="n">
         <v>1.94</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K33" t="n">
@@ -8713,13 +8725,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8746,7 +8758,7 @@
       <c r="I34" t="n">
         <v>3.24</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="K34" t="n">
@@ -8759,13 +8771,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8792,7 +8804,7 @@
       <c r="I35" t="n">
         <v>3.67</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="K35" t="n">
@@ -8805,13 +8817,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8838,7 +8850,7 @@
       <c r="I36" t="n">
         <v>2.22</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="K36" t="n">
@@ -8851,13 +8863,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8884,7 +8896,7 @@
       <c r="I37" t="n">
         <v>2.35</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K37" t="n">
@@ -8897,13 +8909,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8930,7 +8942,7 @@
       <c r="I38" t="n">
         <v>-0.78</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K38" t="n">
@@ -8943,13 +8955,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8976,7 +8988,7 @@
       <c r="I39" t="n">
         <v>-1.57</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K39" t="n">
@@ -8989,13 +9001,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9022,7 +9034,7 @@
       <c r="I40" t="n">
         <v>-1.21</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="K40" t="n">
@@ -9035,13 +9047,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9068,7 +9080,7 @@
       <c r="I41" t="n">
         <v>-0.93</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="K41" t="n">
@@ -9081,13 +9093,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43508</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9114,7 +9126,7 @@
       <c r="I42" t="n">
         <v>0.9900000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43508</v>
       </c>
       <c r="K42" t="n">
@@ -9127,13 +9139,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9160,7 +9172,7 @@
       <c r="I43" t="n">
         <v>2.26</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="K43" t="n">
@@ -9173,13 +9185,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9206,7 +9218,7 @@
       <c r="I44" t="n">
         <v>1.57</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="K44" t="n">
@@ -9219,13 +9231,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9252,7 +9264,7 @@
       <c r="I45" t="n">
         <v>1.28</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K45" t="n">
@@ -9265,13 +9277,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9298,7 +9310,7 @@
       <c r="I46" t="n">
         <v>1.07</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="K46" t="n">
@@ -9311,13 +9323,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9344,7 +9356,7 @@
       <c r="I47" t="n">
         <v>0.36</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K47" t="n">
@@ -9357,13 +9369,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9390,7 +9402,7 @@
       <c r="I48" t="n">
         <v>0.14</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K48" t="n">
@@ -9403,13 +9415,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9436,7 +9448,7 @@
       <c r="I49" t="n">
         <v>0.24</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K49" t="n">
@@ -9449,13 +9461,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9482,7 +9494,7 @@
       <c r="I50" t="n">
         <v>0.54</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="K50" t="n">
@@ -9495,13 +9507,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9528,7 +9540,7 @@
       <c r="I51" t="n">
         <v>1.37</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K51" t="n">
@@ -9541,13 +9553,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9574,7 +9586,7 @@
       <c r="I52" t="n">
         <v>1.08</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="K52" t="n">
@@ -9587,13 +9599,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9620,7 +9632,7 @@
       <c r="I53" t="n">
         <v>1.03</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K53" t="n">
@@ -9633,13 +9645,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44606</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9666,7 +9678,7 @@
       <c r="I54" t="n">
         <v>1.28</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44606</v>
       </c>
       <c r="K54" t="n">
@@ -9679,13 +9691,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9712,7 +9724,7 @@
       <c r="I55" t="n">
         <v>1.29</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K55" t="n">
@@ -9725,13 +9737,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9758,7 +9770,7 @@
       <c r="I56" t="n">
         <v>2.37</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K56" t="n">
@@ -9771,13 +9783,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9804,7 +9816,7 @@
       <c r="I57" t="n">
         <v>2.18</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K57" t="n">
@@ -9817,13 +9829,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9850,7 +9862,7 @@
       <c r="I58" t="n">
         <v>1.54</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="K58" t="n">
@@ -9863,13 +9875,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9896,7 +9908,7 @@
       <c r="I59" t="n">
         <v>1.06</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K59" t="n">
@@ -9909,13 +9921,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9942,7 +9954,7 @@
       <c r="I60" t="n">
         <v>0.73</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K60" t="n">
@@ -9955,13 +9967,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9988,7 +10000,7 @@
       <c r="I61" t="n">
         <v>0.6799999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="K61" t="n">
@@ -10001,13 +10013,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10034,7 +10046,7 @@
       <c r="I62" t="n">
         <v>0.6800000000000002</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="K62" t="n">
@@ -10047,13 +10059,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10080,7 +10092,7 @@
       <c r="I63" t="n">
         <v>0.7200000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10093,13 +10105,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10126,7 +10138,7 @@
       <c r="I64" t="n">
         <v>0.51</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K64" t="n">
@@ -10139,13 +10151,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10172,7 +10184,7 @@
       <c r="I65" t="n">
         <v>0.18</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K65" t="n">
@@ -10185,13 +10197,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10218,7 +10230,7 @@
       <c r="I66" t="n">
         <v>0.58</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K66" t="n">
@@ -10231,13 +10243,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10264,7 +10276,7 @@
       <c r="I67" t="n">
         <v>0.52</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K67" t="n">
@@ -10277,13 +10289,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10310,7 +10322,7 @@
       <c r="I68" t="n">
         <v>0.9400000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K68" t="n">
@@ -10323,13 +10335,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10356,7 +10368,7 @@
       <c r="I69" t="n">
         <v>1.58</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K69" t="n">
@@ -10369,13 +10381,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10402,7 +10414,7 @@
       <c r="I70" t="n">
         <v>1.83</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K70" t="n">
@@ -10415,13 +10427,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10448,7 +10460,7 @@
       <c r="I71" t="n">
         <v>2.08</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K71" t="n">
@@ -10461,13 +10473,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10494,7 +10506,7 @@
       <c r="I72" t="n">
         <v>2.18</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="K72" t="n">
@@ -10531,52 +10543,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39920</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="C2" t="n">
@@ -10605,10 +10617,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40219</v>
       </c>
       <c r="C3" t="n">
@@ -10637,10 +10649,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="C4" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40374</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40389</v>
       </c>
       <c r="C5" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="C6" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40584</v>
       </c>
       <c r="C7" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C8" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="C9" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40833</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C10" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="C11" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41015</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41026</v>
       </c>
       <c r="C12" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C13" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41197</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="C14" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41318</v>
       </c>
       <c r="C15" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41379</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C16" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41470</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C17" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41562</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C18" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41680</v>
       </c>
       <c r="C19" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41744</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41757</v>
       </c>
       <c r="C20" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41835</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C21" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41927</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C22" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="C23" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42109</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C24" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42200</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C25" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42304</v>
       </c>
       <c r="C26" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="C27" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C28" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42578</v>
       </c>
       <c r="C29" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42657</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C30" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="C31" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42838</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42850</v>
       </c>
       <c r="C32" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42930</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42942</v>
       </c>
       <c r="C33" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43021</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C34" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C35" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43203</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C36" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43294</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="C37" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43397</v>
       </c>
       <c r="C38" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43508</v>
       </c>
       <c r="C39" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="C40" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="C41" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43754</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C42" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43871</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="C43" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C44" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44036</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C45" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44126</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C46" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="C47" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C48" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44404</v>
       </c>
       <c r="C49" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C50" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44606</v>
       </c>
       <c r="C51" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44673</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C52" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44762</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C53" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44855</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C54" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44970</v>
       </c>
       <c r="C55" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C56" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45131</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C57" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45229</v>
       </c>
       <c r="C58" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="C59" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45498</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C61" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45589</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C62" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C63" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45771</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C64" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45863</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C65" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45953</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C66" t="n">
@@ -12653,10 +12665,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C67" t="n">
@@ -12685,10 +12697,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C68" t="n">
@@ -12717,10 +12729,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46227</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46232</v>
       </c>
       <c r="C69" t="n">
@@ -12767,12 +12779,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/GLW.xlsx
+++ b/salidas/empresas/GLW.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.94625282287598</v>
+        <v>15.94625091552734</v>
       </c>
       <c r="C2" t="n">
         <v>24.35000038146973</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>15.98554706573486</v>
+        <v>15.98553943634033</v>
       </c>
       <c r="C3" t="n">
         <v>24.40999984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>17.62928199768066</v>
+        <v>17.62928009033203</v>
       </c>
       <c r="C4" t="n">
         <v>26.92000007629395</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.88076305389404</v>
+        <v>15.88076496124268</v>
       </c>
       <c r="C6" t="n">
         <v>24.25</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>15.84146595001221</v>
+        <v>15.84147262573242</v>
       </c>
       <c r="C7" t="n">
         <v>24.19000053405762</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.55790901184082</v>
+        <v>14.5579080581665</v>
       </c>
       <c r="C9" t="n">
         <v>22.22999954223633</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>15.98554706573486</v>
+        <v>15.98553943634033</v>
       </c>
       <c r="C10" t="n">
         <v>24.40999984741211</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>13.37914276123047</v>
+        <v>13.37913513183594</v>
       </c>
       <c r="C11" t="n">
         <v>20.43000030517578</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>14.11914443969727</v>
+        <v>14.11913871765137</v>
       </c>
       <c r="C12" t="n">
         <v>21.55999946594238</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>12.25274848937988</v>
+        <v>12.25273990631104</v>
       </c>
       <c r="C13" t="n">
         <v>18.70999908447266</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.64763450622559</v>
+        <v>13.64763736724854</v>
       </c>
       <c r="C14" t="n">
         <v>20.84000015258789</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>13.51010513305664</v>
+        <v>13.51011085510254</v>
       </c>
       <c r="C15" t="n">
         <v>20.6299991607666</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.89189338684082</v>
+        <v>14.89189529418945</v>
       </c>
       <c r="C16" t="n">
         <v>22.73999977111816</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>15.53367233276367</v>
+        <v>15.53367137908936</v>
       </c>
       <c r="C17" t="n">
         <v>23.71999931335449</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>16.37191200256348</v>
+        <v>16.37191581726074</v>
       </c>
       <c r="C18" t="n">
         <v>25</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.73210525512695</v>
+        <v>16.73210334777832</v>
       </c>
       <c r="C19" t="n">
         <v>25.54999923706055</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>15.61226654052734</v>
+        <v>15.61226463317871</v>
       </c>
       <c r="C20" t="n">
         <v>23.84000015258789</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.17645454406738</v>
+        <v>16.17645263671875</v>
       </c>
       <c r="C22" t="n">
         <v>24.64999961853027</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>15.92708683013916</v>
+        <v>15.92708206176758</v>
       </c>
       <c r="C23" t="n">
         <v>24.27000045776367</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>15.97744750976562</v>
+        <v>15.97744846343994</v>
       </c>
       <c r="C24" t="n">
         <v>24.29000091552734</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>15.78011894226074</v>
+        <v>15.78011417388916</v>
       </c>
       <c r="C25" t="n">
         <v>23.98999977111816</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>15.89193439483643</v>
+        <v>15.89193725585938</v>
       </c>
       <c r="C26" t="n">
         <v>24.15999984741211</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>15.8459005355835</v>
+        <v>15.84589385986328</v>
       </c>
       <c r="C28" t="n">
         <v>24.04000091552734</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>17.60582542419434</v>
+        <v>17.60581016540527</v>
       </c>
       <c r="C29" t="n">
         <v>26.70999908447266</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>18.05386924743652</v>
+        <v>18.05387115478516</v>
       </c>
       <c r="C30" t="n">
         <v>27.34000015258789</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>13.21353244781494</v>
+        <v>13.21353149414062</v>
       </c>
       <c r="C32" t="n">
         <v>20.01000022888184</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>13.59597682952881</v>
+        <v>13.59597873687744</v>
       </c>
       <c r="C33" t="n">
         <v>20.54000091552734</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>10.35253429412842</v>
+        <v>10.35253620147705</v>
       </c>
       <c r="C34" t="n">
         <v>15.64000034332275</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>7.168665409088135</v>
+        <v>7.168666839599609</v>
       </c>
       <c r="C35" t="n">
         <v>10.82999992370605</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>5.996695995330811</v>
+        <v>5.996695041656494</v>
       </c>
       <c r="C36" t="n">
         <v>9.010000228881836</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>6.342786312103271</v>
+        <v>6.342784404754639</v>
       </c>
       <c r="C37" t="n">
         <v>9.529999732971191</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>6.72881031036377</v>
+        <v>6.728808403015137</v>
       </c>
       <c r="C38" t="n">
         <v>10.10999965667725</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>7.055545806884766</v>
+        <v>7.055543899536133</v>
       </c>
       <c r="C39" t="n">
         <v>10.55000019073486</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.874602317810059</v>
+        <v>8.874603271484375</v>
       </c>
       <c r="C40" t="n">
         <v>13.27000045776367</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.777445793151855</v>
+        <v>9.777446746826172</v>
       </c>
       <c r="C41" t="n">
         <v>14.61999988555908</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.77733516693115</v>
+        <v>10.77733612060547</v>
       </c>
       <c r="C43" t="n">
         <v>16.05999946594238</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.40813732147217</v>
+        <v>11.40814304351807</v>
       </c>
       <c r="C44" t="n">
         <v>17</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>10.15131759643555</v>
+        <v>10.15131187438965</v>
       </c>
       <c r="C45" t="n">
         <v>15.07999992370605</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>10.30614566802979</v>
+        <v>10.30614185333252</v>
       </c>
       <c r="C46" t="n">
         <v>15.3100004196167</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>9.834927558898926</v>
+        <v>9.834930419921875</v>
       </c>
       <c r="C47" t="n">
         <v>14.60999965667725</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.03881740570068</v>
+        <v>13.03882312774658</v>
       </c>
       <c r="C49" t="n">
         <v>19.30999946594238</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>11.93910694122314</v>
+        <v>11.93911170959473</v>
       </c>
       <c r="C51" t="n">
         <v>17.6299991607666</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>13.6862964630127</v>
+        <v>13.68629837036133</v>
       </c>
       <c r="C52" t="n">
         <v>20.20999908447266</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.03618144989014</v>
+        <v>13.03618049621582</v>
       </c>
       <c r="C53" t="n">
         <v>19.25</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>11.83859252929688</v>
+        <v>11.83858966827393</v>
       </c>
       <c r="C54" t="n">
         <v>17.43000030517578</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>10.96920394897461</v>
+        <v>10.96920871734619</v>
       </c>
       <c r="C55" t="n">
         <v>16.14999961853027</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>12.30724239349365</v>
+        <v>12.30724048614502</v>
       </c>
       <c r="C56" t="n">
         <v>18.1200008392334</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>10.68299198150635</v>
+        <v>10.68298721313477</v>
       </c>
       <c r="C57" t="n">
         <v>15.68000030517578</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>12.45440578460693</v>
+        <v>12.45440483093262</v>
       </c>
       <c r="C58" t="n">
         <v>18.28000068664551</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>12.45440578460693</v>
+        <v>12.45440483093262</v>
       </c>
       <c r="C59" t="n">
         <v>18.28000068664551</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>12.0648307800293</v>
+        <v>12.06482601165771</v>
       </c>
       <c r="C60" t="n">
         <v>17.65999984741211</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>13.19889736175537</v>
+        <v>13.19889545440674</v>
       </c>
       <c r="C61" t="n">
         <v>19.31999969482422</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>15.78923320770264</v>
+        <v>15.78924465179443</v>
       </c>
       <c r="C63" t="n">
         <v>23.05999946594238</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>14.125412940979</v>
+        <v>14.12540912628174</v>
       </c>
       <c r="C64" t="n">
         <v>20.6299991607666</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>14.33766937255859</v>
+        <v>14.33767318725586</v>
       </c>
       <c r="C65" t="n">
         <v>20.94000053405762</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>13.83208084106445</v>
+        <v>13.83207988739014</v>
       </c>
       <c r="C66" t="n">
         <v>20.14999961853027</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>12.45916557312012</v>
+        <v>12.45916366577148</v>
       </c>
       <c r="C67" t="n">
         <v>18.14999961853027</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>10.92150497436523</v>
+        <v>10.92150592803955</v>
       </c>
       <c r="C68" t="n">
         <v>15.90999984741211</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>10.35344791412354</v>
+        <v>10.35344886779785</v>
       </c>
       <c r="C69" t="n">
         <v>15.02999973297119</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>8.514214515686035</v>
+        <v>8.514212608337402</v>
       </c>
       <c r="C70" t="n">
         <v>12.35999965667725</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>9.843698501586914</v>
+        <v>9.843696594238281</v>
       </c>
       <c r="C71" t="n">
         <v>14.28999996185303</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>9.186427116394043</v>
+        <v>9.18642520904541</v>
       </c>
       <c r="C72" t="n">
         <v>13.27000045776367</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>8.98566722869873</v>
+        <v>8.985668182373047</v>
       </c>
       <c r="C73" t="n">
         <v>12.97999954223633</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>8.909516334533691</v>
+        <v>8.909520149230957</v>
       </c>
       <c r="C74" t="n">
         <v>12.86999988555908</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>9.07671070098877</v>
+        <v>9.076711654663086</v>
       </c>
       <c r="C75" t="n">
         <v>13.03999996185303</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>9.800622940063477</v>
+        <v>9.800620079040527</v>
       </c>
       <c r="C76" t="n">
         <v>14.07999992370605</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>9.988559722900391</v>
+        <v>9.988558769226074</v>
       </c>
       <c r="C77" t="n">
         <v>14.35000038146973</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>9.094744682312012</v>
+        <v>9.094746589660645</v>
       </c>
       <c r="C78" t="n">
         <v>12.98999977111816</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>9.052742004394531</v>
+        <v>9.052737236022949</v>
       </c>
       <c r="C79" t="n">
         <v>12.93000030517578</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>7.988532543182373</v>
+        <v>7.988533973693848</v>
       </c>
       <c r="C80" t="n">
         <v>11.40999984741211</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>9.266267776489258</v>
+        <v>9.266266822814941</v>
       </c>
       <c r="C82" t="n">
         <v>13.14999961853027</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>8.279746055603027</v>
+        <v>8.279742240905762</v>
       </c>
       <c r="C83" t="n">
         <v>11.75</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>8.688047409057617</v>
+        <v>8.688045501708984</v>
       </c>
       <c r="C84" t="n">
         <v>12.22999954223633</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>8.965097427368164</v>
+        <v>8.965096473693848</v>
       </c>
       <c r="C85" t="n">
         <v>12.61999988555908</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>8.524656295776367</v>
+        <v>8.524654388427734</v>
       </c>
       <c r="C86" t="n">
         <v>12</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>9.023754119873047</v>
+        <v>9.02375316619873</v>
       </c>
       <c r="C87" t="n">
         <v>12.60999965667725</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.538989067077637</v>
+        <v>9.538986206054688</v>
       </c>
       <c r="C88" t="n">
         <v>13.32999992370605</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>10.37624740600586</v>
+        <v>10.37624168395996</v>
       </c>
       <c r="C89" t="n">
         <v>14.5</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>11.06905174255371</v>
+        <v>11.06904983520508</v>
       </c>
       <c r="C90" t="n">
         <v>15.36999988555908</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>10.93942356109619</v>
+        <v>10.93942165374756</v>
       </c>
       <c r="C92" t="n">
         <v>15.1899995803833</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.58172988891602</v>
+        <v>10.58173179626465</v>
       </c>
       <c r="C94" t="n">
         <v>14.59000015258789</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>12.39491367340088</v>
+        <v>12.3949146270752</v>
       </c>
       <c r="C95" t="n">
         <v>17.09000015258789</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.46215629577637</v>
+        <v>12.46215152740479</v>
       </c>
       <c r="C96" t="n">
         <v>17.07999992370605</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>13.00208187103271</v>
+        <v>13.0020809173584</v>
       </c>
       <c r="C97" t="n">
         <v>17.81999969482422</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>12.55700588226318</v>
+        <v>12.55700206756592</v>
       </c>
       <c r="C98" t="n">
         <v>17.20999908447266</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>14.13335132598877</v>
+        <v>14.13336277008057</v>
       </c>
       <c r="C99" t="n">
         <v>19.27000045776367</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>15.27018356323242</v>
+        <v>15.270188331604</v>
       </c>
       <c r="C100" t="n">
         <v>20.81999969482422</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>15.3361930847168</v>
+        <v>15.33619403839111</v>
       </c>
       <c r="C101" t="n">
         <v>20.90999984741211</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>15.69544315338135</v>
+        <v>15.6954402923584</v>
       </c>
       <c r="C102" t="n">
         <v>21.29999923706055</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>16.17440986633301</v>
+        <v>16.17441368103027</v>
       </c>
       <c r="C103" t="n">
         <v>21.95000076293945</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>14.47959804534912</v>
+        <v>14.47959899902344</v>
       </c>
       <c r="C104" t="n">
         <v>19.64999961853027</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>15.44569110870361</v>
+        <v>15.4456958770752</v>
       </c>
       <c r="C105" t="n">
         <v>20.86000061035156</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>14.32021522521973</v>
+        <v>14.32021808624268</v>
       </c>
       <c r="C106" t="n">
         <v>19.34000015258789</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>15.12730121612549</v>
+        <v>15.12730026245117</v>
       </c>
       <c r="C107" t="n">
         <v>20.43000030517578</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>15.63931083679199</v>
+        <v>15.63931655883789</v>
       </c>
       <c r="C108" t="n">
         <v>21.02000045776367</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>17.06039237976074</v>
+        <v>17.06039047241211</v>
       </c>
       <c r="C109" t="n">
         <v>22.93000030517578</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>18.24244117736816</v>
+        <v>18.24244689941406</v>
       </c>
       <c r="C111" t="n">
         <v>24.39999961853027</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>16.95650100708008</v>
+        <v>16.95650482177734</v>
       </c>
       <c r="C112" t="n">
         <v>22.68000030517578</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>15.64813041687012</v>
+        <v>15.6481351852417</v>
       </c>
       <c r="C113" t="n">
         <v>20.93000030517578</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>15.72965240478516</v>
+        <v>15.72964954376221</v>
       </c>
       <c r="C114" t="n">
         <v>20.92000007629395</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>14.83489608764648</v>
+        <v>14.83489036560059</v>
       </c>
       <c r="C115" t="n">
         <v>19.72999954223633</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>14.04540538787842</v>
+        <v>14.04539966583252</v>
       </c>
       <c r="C116" t="n">
         <v>18.68000030517578</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>13.03480243682861</v>
+        <v>13.0348014831543</v>
       </c>
       <c r="C117" t="n">
         <v>17.20999908447266</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.96663570404053</v>
+        <v>12.96663856506348</v>
       </c>
       <c r="C118" t="n">
         <v>17.1200008392334</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>14.0875825881958</v>
+        <v>14.08758449554443</v>
       </c>
       <c r="C119" t="n">
         <v>18.60000038146973</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.93429756164551</v>
+        <v>13.93430328369141</v>
       </c>
       <c r="C121" t="n">
         <v>18.28000068664551</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>14.1858491897583</v>
+        <v>14.18585109710693</v>
       </c>
       <c r="C122" t="n">
         <v>18.61000061035156</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>14.05103778839111</v>
+        <v>14.05103588104248</v>
       </c>
       <c r="C123" t="n">
         <v>18.29999923706055</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>16.0396842956543</v>
+        <v>16.0396785736084</v>
       </c>
       <c r="C124" t="n">
         <v>20.88999938964844</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>16.14868927001953</v>
+        <v>16.148681640625</v>
       </c>
       <c r="C126" t="n">
         <v>20.88999938964844</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>15.83174610137939</v>
+        <v>15.83174133300781</v>
       </c>
       <c r="C127" t="n">
         <v>20.47999954223633</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>17.17682266235352</v>
+        <v>17.17681694030762</v>
       </c>
       <c r="C128" t="n">
         <v>22.21999931335449</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>17.64522743225098</v>
+        <v>17.64522552490234</v>
       </c>
       <c r="C129" t="n">
         <v>22.69000053405762</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>18.98303604125977</v>
+        <v>18.98302841186523</v>
       </c>
       <c r="C133" t="n">
         <v>24.27000045776367</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>20.71942520141602</v>
+        <v>20.71943473815918</v>
       </c>
       <c r="C134" t="n">
         <v>26.48999977111816</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>21.2377758026123</v>
+        <v>21.23777770996094</v>
       </c>
       <c r="C136" t="n">
         <v>27</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>22.69295883178711</v>
+        <v>22.69296073913574</v>
       </c>
       <c r="C137" t="n">
         <v>28.85000038146973</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>23.01022148132324</v>
+        <v>23.01021575927734</v>
       </c>
       <c r="C138" t="n">
         <v>29.10000038146973</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>23.76141166687012</v>
+        <v>23.76140975952148</v>
       </c>
       <c r="C139" t="n">
         <v>30.04999923706055</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>22.86459350585938</v>
+        <v>22.86459922790527</v>
       </c>
       <c r="C141" t="n">
         <v>28.76000022888184</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>23.78681373596191</v>
+        <v>23.78681945800781</v>
       </c>
       <c r="C142" t="n">
         <v>29.92000007629395</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>24.94228553771973</v>
+        <v>24.94229316711426</v>
       </c>
       <c r="C146" t="n">
         <v>31.21999931335449</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>23.37363815307617</v>
+        <v>23.37364387512207</v>
       </c>
       <c r="C147" t="n">
         <v>29.07999992370605</v>
@@ -4234,7 +4234,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>22.40911865234375</v>
+        <v>22.40911293029785</v>
       </c>
       <c r="C148" t="n">
         <v>27.8799991607666</v>
@@ -4261,7 +4261,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>21.71787452697754</v>
+        <v>21.71787643432617</v>
       </c>
       <c r="C149" t="n">
         <v>27.02000045776367</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>21.98644256591797</v>
+        <v>21.98643684387207</v>
       </c>
       <c r="C150" t="n">
         <v>27.17000007629395</v>
@@ -4315,7 +4315,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>22.26157760620117</v>
+        <v>22.26157569885254</v>
       </c>
       <c r="C151" t="n">
         <v>27.51000022888184</v>
@@ -4342,7 +4342,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>26.84983825683594</v>
+        <v>26.84984016418457</v>
       </c>
       <c r="C152" t="n">
         <v>33.18000030517578</v>
@@ -4396,7 +4396,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>28.71827697753906</v>
+        <v>28.7182674407959</v>
       </c>
       <c r="C154" t="n">
         <v>35.29999923706055</v>
@@ -4423,7 +4423,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>25.99288558959961</v>
+        <v>25.99288940429688</v>
       </c>
       <c r="C155" t="n">
         <v>31.95000076293945</v>
@@ -4450,7 +4450,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>26.36275863647461</v>
+        <v>26.36276245117188</v>
       </c>
       <c r="C156" t="n">
         <v>32.22000122070312</v>
@@ -4477,7 +4477,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>24.7181568145752</v>
+        <v>24.71815490722656</v>
       </c>
       <c r="C157" t="n">
         <v>30.20999908447266</v>
@@ -4504,7 +4504,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>27.21370506286621</v>
+        <v>27.21369361877441</v>
       </c>
       <c r="C158" t="n">
         <v>33.2599983215332</v>
@@ -4531,7 +4531,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>28.64604187011719</v>
+        <v>28.64603805541992</v>
       </c>
       <c r="C159" t="n">
         <v>34.81000137329102</v>
@@ -4560,7 +4560,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>27.23883438110352</v>
+        <v>27.23883819580078</v>
       </c>
       <c r="C160" t="n">
         <v>33.09999847412109</v>
@@ -4647,7 +4647,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>27.53447532653809</v>
+        <v>27.53446960449219</v>
       </c>
       <c r="C163" t="n">
         <v>33.22999954223633</v>
@@ -4676,7 +4676,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.47953796386719</v>
+        <v>25.47953987121582</v>
       </c>
       <c r="C164" t="n">
         <v>30.75</v>
@@ -4705,7 +4705,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.24639892578125</v>
+        <v>23.24640083312988</v>
       </c>
       <c r="C165" t="n">
         <v>27.85000038146973</v>
@@ -4734,7 +4734,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>23.80564880371094</v>
+        <v>23.80565071105957</v>
       </c>
       <c r="C166" t="n">
         <v>28.52000045776367</v>
@@ -4763,7 +4763,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>24.7321605682373</v>
+        <v>24.73216247558594</v>
       </c>
       <c r="C167" t="n">
         <v>29.6299991607666</v>
@@ -4792,7 +4792,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>24.40622711181641</v>
+        <v>24.40622520446777</v>
       </c>
       <c r="C168" t="n">
         <v>29.04000091552734</v>
@@ -4821,7 +4821,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>24.46506118774414</v>
+        <v>24.46505737304688</v>
       </c>
       <c r="C169" t="n">
         <v>29.11000061035156</v>
@@ -4850,7 +4850,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>22.43120384216309</v>
+        <v>22.43120765686035</v>
       </c>
       <c r="C170" t="n">
         <v>26.69000053405762</v>
@@ -4908,7 +4908,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>17.41425323486328</v>
+        <v>17.41426277160645</v>
       </c>
       <c r="C172" t="n">
         <v>20.54000091552734</v>
@@ -4937,7 +4937,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>18.66055488586426</v>
+        <v>18.66056251525879</v>
       </c>
       <c r="C173" t="n">
         <v>22.01000022888184</v>
@@ -5053,7 +5053,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>27.96999549865723</v>
+        <v>27.96999740600586</v>
       </c>
       <c r="C177" t="n">
         <v>32.45999908447266</v>
@@ -5082,7 +5082,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>27.92691421508789</v>
+        <v>27.92691612243652</v>
       </c>
       <c r="C178" t="n">
         <v>32.40999984741211</v>
@@ -5111,7 +5111,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>27.54777908325195</v>
+        <v>27.54777717590332</v>
       </c>
       <c r="C179" t="n">
         <v>31.96999931335449</v>
@@ -5140,7 +5140,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>32.44227981567383</v>
+        <v>32.44228363037109</v>
       </c>
       <c r="C180" t="n">
         <v>37.41999816894531</v>
@@ -5169,7 +5169,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>31.21116828918457</v>
+        <v>31.21116638183594</v>
       </c>
       <c r="C181" t="n">
         <v>36</v>
@@ -5198,7 +5198,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>31.09846496582031</v>
+        <v>31.09846878051758</v>
       </c>
       <c r="C182" t="n">
         <v>35.86999893188477</v>
@@ -5227,7 +5227,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>33.36045837402344</v>
+        <v>33.36046981811523</v>
       </c>
       <c r="C183" t="n">
         <v>38.2400016784668</v>
@@ -5256,7 +5256,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>37.95798492431641</v>
+        <v>37.9579963684082</v>
       </c>
       <c r="C184" t="n">
         <v>43.5099983215332</v>
@@ -5314,7 +5314,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>38.27243804931641</v>
+        <v>38.27244186401367</v>
       </c>
       <c r="C186" t="n">
         <v>43.63000106811523</v>
@@ -5343,7 +5343,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>35.87766647338867</v>
+        <v>35.87766265869141</v>
       </c>
       <c r="C187" t="n">
         <v>40.90000152587891</v>
@@ -5401,7 +5401,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>35.28725051879883</v>
+        <v>35.28724670410156</v>
       </c>
       <c r="C189" t="n">
         <v>39.9900016784668</v>
@@ -5430,7 +5430,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>32.19883346557617</v>
+        <v>32.19884490966797</v>
       </c>
       <c r="C190" t="n">
         <v>36.4900016784668</v>
@@ -5459,7 +5459,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>31.38702774047852</v>
+        <v>31.38702964782715</v>
       </c>
       <c r="C191" t="n">
         <v>35.56999969482422</v>
@@ -5488,7 +5488,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>32.93508911132812</v>
+        <v>32.93509292602539</v>
       </c>
       <c r="C192" t="n">
         <v>37.09000015258789</v>
@@ -5517,7 +5517,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>33.05940628051758</v>
+        <v>33.05941009521484</v>
       </c>
       <c r="C193" t="n">
         <v>37.22999954223633</v>
@@ -5604,7 +5604,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>32.99516677856445</v>
+        <v>32.99516296386719</v>
       </c>
       <c r="C196" t="n">
         <v>36.90999984741211</v>
@@ -5633,7 +5633,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>31.45759201049805</v>
+        <v>31.45759582519531</v>
       </c>
       <c r="C197" t="n">
         <v>35.18999862670898</v>
@@ -5662,7 +5662,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>32.26815795898438</v>
+        <v>32.26815414428711</v>
       </c>
       <c r="C198" t="n">
         <v>35.81999969482422</v>
@@ -5691,7 +5691,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>28.38552284240723</v>
+        <v>28.38552474975586</v>
       </c>
       <c r="C199" t="n">
         <v>31.51000022888184</v>
@@ -5720,7 +5720,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>33.11493682861328</v>
+        <v>33.11494064331055</v>
       </c>
       <c r="C200" t="n">
         <v>36.7599983215332</v>
@@ -5778,7 +5778,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>26.34947776794434</v>
+        <v>26.34947967529297</v>
       </c>
       <c r="C202" t="n">
         <v>29.02000045776367</v>
@@ -5807,7 +5807,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>29.20960426330566</v>
+        <v>29.20960807800293</v>
       </c>
       <c r="C203" t="n">
         <v>32.16999816894531</v>
@@ -5894,7 +5894,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>31.6805591583252</v>
+        <v>31.6805534362793</v>
       </c>
       <c r="C206" t="n">
         <v>34.61000061035156</v>
@@ -5923,7 +5923,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>31.33212089538574</v>
+        <v>31.33211898803711</v>
       </c>
       <c r="C207" t="n">
         <v>33.95000076293945</v>
@@ -5952,7 +5952,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>32.5595588684082</v>
+        <v>32.55956649780273</v>
       </c>
       <c r="C208" t="n">
         <v>35.27999877929688</v>
@@ -5981,7 +5981,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>30.65840721130371</v>
+        <v>30.65840530395508</v>
       </c>
       <c r="C209" t="n">
         <v>33.22000122070312</v>
@@ -6010,7 +6010,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>28.68901634216309</v>
+        <v>28.68901443481445</v>
       </c>
       <c r="C210" t="n">
         <v>30.80999946594238</v>
@@ -6039,7 +6039,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>32.62781524658203</v>
+        <v>32.6278190612793</v>
       </c>
       <c r="C211" t="n">
         <v>35.04000091552734</v>
@@ -6068,7 +6068,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>31.60354042053223</v>
+        <v>31.60354614257812</v>
       </c>
       <c r="C212" t="n">
         <v>33.93999862670898</v>
@@ -6097,7 +6097,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>30.82296752929688</v>
+        <v>30.82297134399414</v>
       </c>
       <c r="C213" t="n">
         <v>32.81999969482422</v>
@@ -6155,7 +6155,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>25.13170623779297</v>
+        <v>25.1317081451416</v>
       </c>
       <c r="C215" t="n">
         <v>26.76000022888184</v>
@@ -6242,7 +6242,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>30.8110523223877</v>
+        <v>30.81104850769043</v>
       </c>
       <c r="C218" t="n">
         <v>32.4900016784668</v>
@@ -6300,7 +6300,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>31.52897834777832</v>
+        <v>31.52898025512695</v>
       </c>
       <c r="C220" t="n">
         <v>32.95999908447266</v>
@@ -6329,7 +6329,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>31.93074607849121</v>
+        <v>31.93074989318848</v>
       </c>
       <c r="C221" t="n">
         <v>33.38000106811523</v>
@@ -6358,7 +6358,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>35.91436386108398</v>
+        <v>35.91437149047852</v>
       </c>
       <c r="C222" t="n">
         <v>37.2599983215332</v>
@@ -6387,7 +6387,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>37.44694519042969</v>
+        <v>37.44694900512695</v>
       </c>
       <c r="C223" t="n">
         <v>38.84999847412109</v>
@@ -6416,7 +6416,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>38.5650520324707</v>
+        <v>38.56505584716797</v>
       </c>
       <c r="C224" t="n">
         <v>40.0099983215332</v>
@@ -6474,7 +6474,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>43.81241607666016</v>
+        <v>43.81241226196289</v>
       </c>
       <c r="C226" t="n">
         <v>45.15000152587891</v>
@@ -6503,7 +6503,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>46.18013000488281</v>
+        <v>46.18012619018555</v>
       </c>
       <c r="C227" t="n">
         <v>47.59000015258789</v>
@@ -6532,7 +6532,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>47.51087188720703</v>
+        <v>47.5108757019043</v>
       </c>
       <c r="C228" t="n">
         <v>48.66999816894531</v>
@@ -6561,7 +6561,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>46.38826370239258</v>
+        <v>46.38825988769531</v>
       </c>
       <c r="C229" t="n">
         <v>47.52000045776367</v>
@@ -6619,7 +6619,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>49.23698425292969</v>
+        <v>49.23698043823242</v>
       </c>
       <c r="C231" t="n">
         <v>50.15000152587891</v>
@@ -6648,7 +6648,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>44.94653701782227</v>
+        <v>44.94654083251953</v>
       </c>
       <c r="C232" t="n">
         <v>45.77999877929688</v>
@@ -6677,7 +6677,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>43.5720329284668</v>
+        <v>43.572021484375</v>
       </c>
       <c r="C233" t="n">
         <v>44.38000106811523</v>
@@ -6706,7 +6706,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>48.96158218383789</v>
+        <v>48.96157836914062</v>
       </c>
       <c r="C234" t="n">
         <v>49.59000015258789</v>
@@ -6822,7 +6822,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>81.32082366943359</v>
+        <v>81.32083129882812</v>
       </c>
       <c r="C238" t="n">
         <v>82.02999877929688</v>
@@ -6967,7 +6967,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>149.86767578125</v>
+        <v>149.8676910400391</v>
       </c>
       <c r="C243" t="n">
         <v>150.3800048828125</v>
@@ -6996,7 +6996,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>135.5067596435547</v>
+        <v>135.5067749023438</v>
       </c>
       <c r="C244" t="n">
         <v>135.9700012207031</v>
@@ -7025,7 +7025,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>163.6804504394531</v>
+        <v>163.6804656982422</v>
       </c>
       <c r="C245" t="n">
         <v>164.2400054931641</v>
